--- a/data/trans_camb/IP16A10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-37,85; -2,06</t>
+          <t>-39,45; -3,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-38,66; -4,36</t>
+          <t>-41,71; -4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 7,3</t>
+          <t>-17,26; 7,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 0,0</t>
+          <t>-23,08; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 0,47</t>
+          <t>-20,89; 1,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -4,25</t>
+          <t>-24,3; -4,34</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 5,88</t>
+          <t>-18,11; 5,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 0,0</t>
+          <t>-22,07; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 3,37</t>
+          <t>-11,44; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 12,54</t>
+          <t>-6,78; 12,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 2,67</t>
+          <t>-10,1; 2,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 2,7</t>
+          <t>-10,37; 3,37</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 0,0</t>
+          <t>-20,21; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 5,13</t>
+          <t>-16,28; 4,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 0,0</t>
+          <t>-20,63; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 4,51</t>
+          <t>-17,12; 4,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -1,55</t>
+          <t>-13,5; -1,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 2,8</t>
+          <t>-11,17; 2,84</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,53</t>
+          <t>0,0; 29,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 0,0</t>
+          <t>-30,53; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 0,0</t>
+          <t>-36,6; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 0,0</t>
+          <t>-13,64; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 0,0</t>
+          <t>-13,74; 0,0</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 7,51</t>
+          <t>-9,42; 7,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,79</t>
+          <t>-6,28; 9,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 4,52</t>
+          <t>-10,88; 4,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 0,0</t>
+          <t>-13,78; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,04</t>
+          <t>-6,24; 4,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,42</t>
+          <t>-5,9; 4,04</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 4,89</t>
+          <t>-11,01; 4,8</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 0,0</t>
+          <t>-15,24; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,57</t>
+          <t>-2,36; 6,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 0,0</t>
+          <t>-5,32; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -0,62</t>
+          <t>-7,56; -0,71</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -1,65</t>
+          <t>-7,94; -1,54</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,8</t>
+          <t>-2,17; 3,12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,79</t>
+          <t>-2,93; 1,82</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,28</t>
+          <t>-3,86; 0,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,46</t>
+          <t>-4,49; -0,49</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 0,29</t>
+          <t>-91,65; -6,11</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -26,48</t>
+          <t>-95,06; -31,45</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 420,35</t>
+          <t>-71,11; 662,14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-76,16; 19,48</t>
+          <t>-77,19; 16,97</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-87,83; -7,41</t>
+          <t>-88,89; -7,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,45; -3,51</t>
+          <t>-39,81; -2,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -4,71</t>
+          <t>-38,72; -4,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 7,17</t>
+          <t>-19,11; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 0,0</t>
+          <t>-30,93; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 1,63</t>
+          <t>-21,27; 0,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,3; -4,34</t>
+          <t>-25,08; -4,23</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 131,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 5,72</t>
+          <t>-17,89; 4,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 0,0</t>
+          <t>-19,39; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,28</t>
+          <t>-11,44; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 12,23</t>
+          <t>-6,73; 12,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 2,74</t>
+          <t>-10,34; 2,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 3,37</t>
+          <t>-10,43; 2,59</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 260,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 0,0</t>
+          <t>-20,77; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 4,92</t>
+          <t>-17,0; 4,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 0,0</t>
+          <t>-19,97; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 4,45</t>
+          <t>-16,24; 4,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -1,57</t>
+          <t>-14,29; -1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 2,84</t>
+          <t>-10,69; 2,88</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,75</t>
+          <t>0,0; 29,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>0,0; 12,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 0,0</t>
+          <t>-25,67; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 0,0</t>
+          <t>-27,78; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 0,0</t>
+          <t>-15,0; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 0,0</t>
+          <t>-13,49; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 7,72</t>
+          <t>-12,37; 5,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,67</t>
+          <t>-6,28; 9,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 4,51</t>
+          <t>-8,28; 4,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 0,0</t>
+          <t>-13,4; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 4,55</t>
+          <t>-6,45; 4,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,04</t>
+          <t>-5,93; 4,28</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 4,8</t>
+          <t>-10,22; 4,94</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 0,0</t>
+          <t>-14,17; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>0,0; 12,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 6,1</t>
+          <t>-2,39; 6,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,0</t>
+          <t>-7,0; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,71</t>
+          <t>-7,67; -0,85</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -1,54</t>
+          <t>-8,47; -1,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,12</t>
+          <t>-2,55; 2,59</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,82</t>
+          <t>-2,94; 1,81</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,2</t>
+          <t>-3,74; 0,29</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,49</t>
+          <t>-4,26; -0,47</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-91,65; -6,11</t>
+          <t>-90,95; -11,08</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-95,06; -31,45</t>
+          <t>-100,0; -29,04</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 662,14</t>
+          <t>-80,52; 446,25</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 320,71</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-77,19; 16,97</t>
+          <t>-76,9; 16,56</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-88,89; -7,86</t>
+          <t>-88,33; -8,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A10-Provincia-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,65</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-15,7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-18,32</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,04</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -2,82</t>
+          <t>-18,13; 7,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-38,72; -4,44</t>
+          <t>-29,07; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 7,26</t>
+          <t>-37,85; -2,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 0,0</t>
+          <t>-38,66; -4,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 0,26</t>
+          <t>-21,71; 0,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,08; -4,23</t>
+          <t>-24,97; -4,25</t>
         </is>
       </c>
     </row>
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-36,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-85,72%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-36,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 131,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-3,46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-7,33</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 4,48</t>
+          <t>-13,01; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 0,0</t>
+          <t>-7,33; 12,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,33</t>
+          <t>-17,71; 5,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 12,53</t>
+          <t>-22,23; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 2,78</t>
+          <t>-11,7; 2,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,59</t>
+          <t>-10,81; 2,7</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-48,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-47,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-48,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 260,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,82</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-6,4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-3,11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 0,0</t>
+          <t>-20,82; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 4,83</t>
+          <t>-16,79; 4,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 0,0</t>
+          <t>-22,57; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 4,46</t>
+          <t>-14,64; 5,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,29; -1,55</t>
+          <t>-13,56; -1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 2,88</t>
+          <t>-10,51; 2,8</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>-44,85%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-48,61%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-44,85%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,07</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-5,01</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-5,01</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,61; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-25,51; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 0,0</t>
+          <t>-13,66; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 0,0</t>
+          <t>-13,36; 0,0</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,52</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,73</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,28</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,02</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-2,73</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 5,67</t>
+          <t>-9,25; 4,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,69</t>
+          <t>-13,59; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 4,47</t>
+          <t>-9,47; 7,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 0,0</t>
+          <t>-6,27; 9,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 4,47</t>
+          <t>-6,06; 4,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 4,28</t>
+          <t>-5,9; 4,42</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-19,15%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-9,03%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-19,15%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-4,25</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 4,94</t>
+          <t>0,0; 12,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,12</t>
+          <t>-10,28; 4,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,44; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 6,21</t>
+          <t>-3,04; 5,57</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,0</t>
+          <t>-6,16; 0,0</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-43,75%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-3,66</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-4,34</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,85</t>
+          <t>-2,52; 2,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -1,57</t>
+          <t>-3,25; 1,79</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,59</t>
+          <t>-7,41; -0,62</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,81</t>
+          <t>-8,43; -1,65</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,29</t>
+          <t>-3,68; 0,28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,47</t>
+          <t>-4,32; -0,46</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-26,32%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-67,5%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-80,02%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-26,32%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -11,08</t>
+          <t>-77,32; 420,35</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 446,25</t>
+          <t>-90,2; 0,29</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 320,71</t>
+          <t>-95,53; -26,48</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 16,56</t>
+          <t>-76,16; 19,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-88,33; -8,58</t>
+          <t>-87,83; -7,41</t>
         </is>
       </c>
     </row>
